--- a/reports/jobs_2026-09-15.xlsx
+++ b/reports/jobs_2026-09-15.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,27 +520,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t xml:space="preserve">Software Engineer - Fullstack </t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/f8649b65-be80-43fc-8abb-4f4d3ceb2984</t>
+          <t>https://www.okta.com/company/careers/opportunity/8203483?gh_jid=8203483</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -565,57 +565,61 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Agnikul Cosmos</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Sarvam AI</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Audio–Video Editor (AI Dubbing Pipeline)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>https://agnikul.in/careers</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sarvam/8925c0ea-ab20-4971-b427-9a44e93d932b</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -628,11 +632,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -640,12 +640,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -816,7 +816,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -824,7 +828,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +850,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -859,11 +863,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -906,7 +906,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -914,7 +918,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -936,12 +940,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -957,7 +961,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -979,12 +983,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1017,12 +1021,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1043,12 +1047,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1060,17 +1064,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Compiler Engineer (Machine Learning)</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1078,7 +1082,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1086,12 +1094,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1103,12 +1111,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1121,11 +1129,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1133,12 +1137,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1155,12 +1159,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1176,7 +1180,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1193,17 +1197,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t xml:space="preserve">IT B2B/EDI Developer </t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1211,7 +1215,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1219,12 +1227,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000148716589</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1236,17 +1244,17 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IT B2B/EDI Developer </t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1266,12 +1274,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000148716589</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1283,17 +1291,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1303,7 +1311,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1313,12 +1321,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1335,12 +1343,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1350,7 +1358,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1360,7 +1368,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1382,12 +1390,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru/Gurugram Full-time</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1407,7 +1415,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1429,7 +1437,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1444,7 +1452,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru/Gurugram Full-time</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1454,7 +1462,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1476,12 +1484,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1489,11 +1497,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1501,7 +1505,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1523,12 +1527,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1536,7 +1540,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1544,7 +1552,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1566,7 +1574,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1591,7 +1599,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1613,7 +1621,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1638,7 +1646,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1660,12 +1668,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1685,7 +1693,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1707,12 +1715,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1732,7 +1740,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1749,17 +1757,17 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1769,7 +1777,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1779,12 +1787,12 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1801,7 +1809,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1848,7 +1856,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1873,7 +1881,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1890,17 +1898,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1908,11 +1916,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1920,12 +1924,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1937,17 +1941,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1963,12 +1967,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Mumbai/Gen-AI-Engineer_SR-45659-1</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1980,17 +1984,17 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2006,12 +2010,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Data-Engineer_SR-43347</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2023,17 +2027,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer- WD</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2041,7 +2045,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2049,12 +2057,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2066,17 +2074,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2084,7 +2092,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2092,12 +2104,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2109,17 +2121,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2127,7 +2139,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2135,12 +2151,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2152,17 +2168,17 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Full-Stack Intern - B2B</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2170,7 +2186,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2178,12 +2198,12 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000148960832</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2195,17 +2215,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2215,7 +2235,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2225,12 +2245,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2242,17 +2262,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2262,7 +2282,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2272,12 +2292,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2289,17 +2309,17 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2307,11 +2327,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2319,12 +2335,12 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2336,17 +2352,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Full-Stack Intern - B2B</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2354,11 +2370,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2366,12 +2378,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000148960832</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2383,12 +2395,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2403,7 +2415,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2413,12 +2425,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2430,17 +2442,17 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2448,11 +2460,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2460,12 +2468,12 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -2477,17 +2485,17 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2495,7 +2503,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2503,12 +2515,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2520,12 +2532,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2538,7 +2550,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2546,12 +2562,12 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=7922676</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
@@ -2563,12 +2579,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2583,7 +2599,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2593,12 +2609,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2610,17 +2626,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2636,12 +2652,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2653,27 +2669,27 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Okta India</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t xml:space="preserve">Cloud Engineer </t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1+ years</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bengaluru, India</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2683,12 +2699,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2700,17 +2716,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2718,11 +2734,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2730,12 +2742,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=7922676</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2747,17 +2759,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2767,7 +2779,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2777,12 +2789,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8167389</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2794,17 +2806,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2812,7 +2824,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2820,12 +2836,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2837,27 +2853,27 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Okta India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cloud Engineer </t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1+ years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, India</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2867,12 +2883,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/opportunity/8003315?gh_jid=8003315</t>
+          <t>https://jobs.lever.co/paytm/f8649b65-be80-43fc-8abb-4f4d3ceb2984</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/okta</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2884,12 +2900,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>Product Management - Intern - Telco.</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2902,7 +2918,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2910,12 +2930,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2932,7 +2952,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Product Management Intern- Insurance</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2942,12 +2962,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>recent graduate</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2957,7 +2977,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2979,7 +2999,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3004,7 +3024,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3026,7 +3046,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3041,7 +3061,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3051,7 +3071,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3073,7 +3093,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern- Insurance</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3083,12 +3103,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3098,7 +3118,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4a97658f-ac6f-4a86-b483-ae50dd5c7a46</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3115,17 +3135,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3133,11 +3153,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3145,12 +3161,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3162,17 +3178,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3182,7 +3198,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -3192,12 +3208,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3209,17 +3225,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3229,7 +3245,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3239,12 +3255,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3256,17 +3272,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3274,7 +3290,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3282,12 +3302,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3299,17 +3319,17 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3317,11 +3337,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3329,12 +3345,12 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3346,17 +3362,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3366,7 +3382,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3376,12 +3392,12 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3393,17 +3409,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3413,7 +3429,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3423,12 +3439,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3440,17 +3456,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3458,7 +3474,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3466,12 +3486,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3488,7 +3508,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3513,7 +3533,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3530,17 +3550,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3550,7 +3570,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -3560,12 +3580,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3577,12 +3597,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3595,11 +3615,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3607,12 +3623,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3624,17 +3640,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Creative Producer - AI</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3642,11 +3658,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3654,12 +3666,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3671,27 +3683,27 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strategy and Operations Intern </t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>recent graduate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3701,12 +3713,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/6d849a05-e924-4aef-a6a4-f5e082358517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3718,17 +3730,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3748,12 +3760,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3765,17 +3777,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3791,12 +3803,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3808,17 +3820,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Creative Producer - AI</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3826,7 +3838,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -3834,12 +3850,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3851,17 +3867,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3871,7 +3887,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3881,12 +3897,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3898,17 +3914,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Unacademy</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3918,7 +3934,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, in</t>
+          <t>Bengaluru, in</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3928,12 +3944,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3942,192 +3958,8 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>Sprinklr</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Internship and Early Careers</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sprinklr.com/careers/</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Stripe India</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Intern</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Test Jerin</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Software (General)</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Unacademy</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I80"/>
+  <autoFilter ref="A1:I76"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4204,10 +4036,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4219,7 +4047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4347,55 +4175,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Darwinbox</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://darwinbox.com/careers</t>
+          <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FarEye</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://fareye.com/careers</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://fareye.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4404,18 +4192,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4424,18 +4212,38 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MakeMyTrip</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://careers.makemytrip.com/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://careers.makemytrip.com/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4444,38 +4252,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MakeMyTrip</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://careers.makemytrip.com/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://careers.makemytrip.com/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4484,18 +4272,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4504,18 +4292,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4524,18 +4312,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
